--- a/disease_registry/outputs/Sugarcane/internet.xlsx
+++ b/disease_registry/outputs/Sugarcane/internet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Disease Registry" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,20 +456,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yellow_Spot</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Mycovellosiella koepkei</t>
-        </is>
-      </c>
+          <t>Yellow_Leaf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -479,32 +475,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yellow_Leaf</t>
+          <t>Yellow_Spot</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sugarcane yellow leaf virus (SCYLV)</t>
+          <t>Mycovellosiella koepkei</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>leaves, midribs, crown</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Mild to severe yellowing of midribs in both young and mature leaves, progressing to leaf necrosis, complete leaf drying, stunting and poor plant growth in severe cases.. Yellowing specifically of the midribs (leaf veins), necrosis progressing from leaf tip to base, clustering of leaves at the crown, shortened internodes, and in severe cases, complete drying and stunting. streak disease, Fiji disease, fleck leaf disease, mosaic disease</t>
-        </is>
-      </c>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -514,67 +502,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sugarcane_Mosaic_Virus</t>
+          <t>Pokkah_Boeng</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sugarcane mosaic virus</t>
+          <t>Fusarium moniliforme</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Root, Vascular, Whole plant</t>
+          <t>Foliar, Stem, Whole plant</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leaves exhibit irregular yellow and green mosaic patterns (inlays, stripes, and mottles) alternating with parallel veins, clearly visible against sunlight. Severely infected leaves turn yellow or yellow-white with red punctate necrosis or abnormally twisted tips. Large yellow or light green areas without small streaks are also characteristic.. Yellow and green mosaic pattern (inlays, stripes, and mottles) alternating with parallel veins on symptomatic leaves, distinctly visible against sunlight; large yellow or light green areas without small streaks (distinguishing from SCSMV which shows numerous small streaks).. sugarcane streak mosaic virus (SCSMV), sorghum mosaic virus (SrMV), maize yellow mosaic virus, sugarcane mild mosaic virus, sugarcane striate mosaic associated virus, maize striate mosaic virus</t>
+          <t>Disease develops in three phases: chlorotic patches on young leaves, top rot with malformation and twisting of leaves, and knife cut stage with transverse cuts in the stalk rind.. Three distinct phases: (1) chlorotic patches at the base of young leaves with wrinkled, twisted, shortened leaves; (2) top rot phase with pronounced malformation, red specks dissolved, rotten and dried spindle base; (3) knife cut stage showing transverse cuts in the rind of the stalk, with large conspicuous chlorotic patches on stalks when leaves are stripped.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Streak_Mosaic_Scsmv</t>
+          <t>Sett_Rot</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sugarcane streak mosaic virus</t>
+          <t>Ceratocystis paradoxa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Fungal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foliar</t>
+          <t>Stem, Whole plant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Patterns of green color on leaf lamina with longitudinal, yellow-green interveinal streaks (3 to 40 mm long) and light and dark green islands.. Numerous streaks of various sizes on leaves, unlike SCMV which shows large areas without small streaks.. sugarcane mosaic virus (SCMV), sorghum mosaic virus (SrMV), maize yellow mosaic virus, sugarcane mild mosaic virus, sugarcane striate mosaic associated virus, maize striate mosaic virus</t>
+          <t>Affected sett tissues develop a reddish colour turning brownish black, with internodal cavities covered with mycelium and spores, and a characteristic pineapple smell. Infected shoots are stunted and may die.. Characteristic pineapple smell associated with rotting tissues; tissues first reddish then brownish black; internodal cavities covered with mycelium and abundant spores.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -584,28 +572,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grassy_Shoot</t>
+          <t>Leaf_Scald</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phytoplasma</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Xanthomonas albilineans</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Foliar, Stem, Vascular, Whole plant</t>
+          <t>Foliar, Whole plant</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Plants exhibit numerous lanky tillers from the base with pale yellow to completely chlorotic, thin and narrow leaves, appearing bushy and grass-like due to reduced internode length and premature continuous tillering.. Grass-like bushy appearance with severely reduced internode length, premature and continuous tillering from plant base, chlorotic thin narrow leaves, stunted clumps with papery abnormally elongated buds on canes, aerial roots at lower nodes.</t>
+          <t>White pencil line (1-2 mm wide) on leaf extending from midrib to margin parallel to veins, with diffuse yellow border. Disease progresses to brown necrosis from leaf tip or margin. Leaves look burned and curl inward, giving a scalded appearance, ultimately killing the entire plant.. White pencil line 1-2 mm wide extending from midrib to leaf margin parallel to veins; diffuse yellow border of varying widths parallel to pencil line; possible reddish discoloration along part of the pencil line; necrosis from leaf tip or margin; leaves look burned and curl inward.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -615,44 +607,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brown_Spot</t>
+          <t>Grassy_Shoot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cercospora longipes E.J. Butler</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Candidatus Phytoplasma sacchari</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bacterial (Phytoplasma)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Foliar</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Foliar, Stem, Vascular, Whole plant</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>The disease is characterised by the production of numerous lanky tillers from the base of the affected shoots. Leaves become pale yellow to completely chlorotic, thin and narrow. The plants appear bushy and 'grass-like' due to reduction in the length of internodes, premature and continuous tillering. Infected plants may produce up to 20 grassy shoots, reducing cane yield and quality.. Production of numerous lanky tillers from the base giving a bushy grass-like appearance; leaves pale yellow to completely chlorotic, thin and narrow; shortened internodes with premature proliferation of axillary buds; canes if formed are thin with aerial roots at lower nodes and papery abnormally elongated buds. Symptoms appear in random, isolated areas in the field distinguishing them from iron deficiency.. Iron deficiency</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Leaf_Scald</t>
+          <t>Sugarcane_Mosaic_Virus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xanthomonas albilineans</t>
+          <t>Sugarcane mosaic virus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leaf scald presents as a white pencil line on leaves extending from the midrib to the margin with a diffuse yellow border, progressing to brown dead tissue that causes leaves to look burned and curl inward.. White pencil line (1-2 mm wide) extending from midrib to leaf margin parallel to veins, diffuse yellow border, reddish discoloration along the pencil line, and brown necrosis developing from leaf tip or margin creating a scalded appearance.</t>
+          <t>Contrasting shades of green on leaves with islands of normal green on a background of paler green or yellowish chlorotic areas, sometimes with leaf reddening or necrosis.. Pattern of contrasting shades of green with islands of normal green on paler green or yellowish chlorotic background; chlorotic areas most evident at base of leaf; may also appear on leaf sheath but rarely on stalk; may be accompanied by leaf reddening or necrosis. Chlorotic areas may be diffuse or sharply defined depending on the clone and virus strain.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -677,67 +677,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sett_Rot</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ceratocystis paradoxa</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Fungal</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Seed, Stem</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Affected tissues develop a reddish colour turning brownish black in later stages, with internodal cavities covered by mycelium and spores, accompanied by a characteristic pineapple smell.. Characteristic pineapple smell associated with rotting tissues and internodal cavities covered with mycelium and abundant spores.</t>
-        </is>
-      </c>
+          <t>Brown_Spot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pokkah_Boeng</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Fusarium species complex (Fusarium sacchari, Fusarium proliferatum, Fusarium verticillioides)</t>
-        </is>
-      </c>
+          <t>Streak_Mosaic_Scsmv</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Foliar, Stem</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Disease exhibits multiple phases: chlorotic phase with rough, wrinkled, twisted, and shortened leaves; top rot phase where the growing point is killed and the entire top of the plant dies; and knife cut phase with characteristic stem damage.. The knife cut phase produces characteristic stem damage appearing as if tissues were removed with a sharp knife, distinguishing it from other diseases.</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
